--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G344"/>
+  <dimension ref="A1:G345"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10470,6 +10470,39 @@
         </is>
       </c>
     </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>8</v>
+      </c>
+      <c r="C345" t="n">
+        <v>11</v>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G345"/>
+  <dimension ref="A1:G346"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10503,6 +10503,39 @@
         </is>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>10</v>
+      </c>
+      <c r="C346" t="n">
+        <v>12</v>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G346"/>
+  <dimension ref="A1:G347"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10536,6 +10536,39 @@
         </is>
       </c>
     </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>10</v>
+      </c>
+      <c r="C347" t="n">
+        <v>12</v>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G347"/>
+  <dimension ref="A1:G348"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10569,6 +10569,39 @@
         </is>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>10</v>
+      </c>
+      <c r="C348" t="n">
+        <v>12</v>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G348"/>
+  <dimension ref="A1:G349"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10602,6 +10602,39 @@
         </is>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>10</v>
+      </c>
+      <c r="C349" t="n">
+        <v>12</v>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G349"/>
+  <dimension ref="A1:G350"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10635,6 +10635,39 @@
         </is>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>10</v>
+      </c>
+      <c r="C350" t="n">
+        <v>13</v>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G350"/>
+  <dimension ref="A1:G351"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10668,6 +10668,39 @@
         </is>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>10</v>
+      </c>
+      <c r="C351" t="n">
+        <v>13</v>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G351"/>
+  <dimension ref="A1:G352"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10701,6 +10701,39 @@
         </is>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>9</v>
+      </c>
+      <c r="C352" t="n">
+        <v>12</v>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G352"/>
+  <dimension ref="A1:G353"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10734,6 +10734,39 @@
         </is>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>9</v>
+      </c>
+      <c r="C353" t="n">
+        <v>12</v>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G353"/>
+  <dimension ref="A1:G354"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10767,6 +10767,37 @@
         </is>
       </c>
     </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>9</v>
+      </c>
+      <c r="C354" t="n">
+        <v>13</v>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>22</v>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G354"/>
+  <dimension ref="A1:G355"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10798,6 +10798,37 @@
         </is>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>10</v>
+      </c>
+      <c r="C355" t="n">
+        <v>14</v>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>22</v>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G355"/>
+  <dimension ref="A1:G356"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10829,6 +10829,37 @@
         </is>
       </c>
     </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>11</v>
+      </c>
+      <c r="C356" t="n">
+        <v>15</v>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>22</v>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G356"/>
+  <dimension ref="A1:G357"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10860,6 +10860,37 @@
         </is>
       </c>
     </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>11</v>
+      </c>
+      <c r="C357" t="n">
+        <v>15</v>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>22</v>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G357"/>
+  <dimension ref="A1:G358"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10891,6 +10891,37 @@
         </is>
       </c>
     </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>10</v>
+      </c>
+      <c r="C358" t="n">
+        <v>15</v>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>23</v>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G358"/>
+  <dimension ref="A1:G359"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10922,6 +10922,37 @@
         </is>
       </c>
     </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>10</v>
+      </c>
+      <c r="C359" t="n">
+        <v>15</v>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>23</v>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G359"/>
+  <dimension ref="A1:G360"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10953,6 +10953,37 @@
         </is>
       </c>
     </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>10</v>
+      </c>
+      <c r="C360" t="n">
+        <v>17</v>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>23</v>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G360"/>
+  <dimension ref="A1:G361"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10984,6 +10984,37 @@
         </is>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>9</v>
+      </c>
+      <c r="C361" t="n">
+        <v>17</v>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>26</v>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G361"/>
+  <dimension ref="A1:G362"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11015,6 +11015,37 @@
         </is>
       </c>
     </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>9</v>
+      </c>
+      <c r="C362" t="n">
+        <v>18</v>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>22</v>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G362"/>
+  <dimension ref="A1:G363"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11046,6 +11046,37 @@
         </is>
       </c>
     </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>9</v>
+      </c>
+      <c r="C363" t="n">
+        <v>17</v>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>23</v>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G363"/>
+  <dimension ref="A1:G364"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11077,6 +11077,37 @@
         </is>
       </c>
     </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>8</v>
+      </c>
+      <c r="C364" t="n">
+        <v>16</v>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>23</v>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G364"/>
+  <dimension ref="A1:G365"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11108,6 +11108,37 @@
         </is>
       </c>
     </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>8</v>
+      </c>
+      <c r="C365" t="n">
+        <v>16</v>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>24</v>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G365"/>
+  <dimension ref="A1:G366"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11139,6 +11139,37 @@
         </is>
       </c>
     </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>8</v>
+      </c>
+      <c r="C366" t="n">
+        <v>16</v>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>26</v>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G366"/>
+  <dimension ref="A1:G367"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11170,6 +11170,37 @@
         </is>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>8</v>
+      </c>
+      <c r="C367" t="n">
+        <v>18</v>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>27</v>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G367"/>
+  <dimension ref="A1:G368"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11201,6 +11201,37 @@
         </is>
       </c>
     </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>8</v>
+      </c>
+      <c r="C368" t="n">
+        <v>19</v>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>27</v>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G368"/>
+  <dimension ref="A1:G369"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11232,6 +11232,37 @@
         </is>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>9</v>
+      </c>
+      <c r="C369" t="n">
+        <v>23</v>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>27</v>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G369"/>
+  <dimension ref="A1:G370"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11263,6 +11263,37 @@
         </is>
       </c>
     </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>7</v>
+      </c>
+      <c r="C370" t="n">
+        <v>24</v>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>28</v>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G370"/>
+  <dimension ref="A1:G371"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11294,6 +11294,37 @@
         </is>
       </c>
     </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>6</v>
+      </c>
+      <c r="C371" t="n">
+        <v>22</v>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>28</v>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G371"/>
+  <dimension ref="A1:G372"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11325,6 +11325,37 @@
         </is>
       </c>
     </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>6</v>
+      </c>
+      <c r="C372" t="n">
+        <v>22</v>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>29</v>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G372"/>
+  <dimension ref="A1:G373"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11356,6 +11356,37 @@
         </is>
       </c>
     </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>5</v>
+      </c>
+      <c r="C373" t="n">
+        <v>22</v>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>29</v>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G373"/>
+  <dimension ref="A1:G374"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11387,6 +11387,37 @@
         </is>
       </c>
     </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>5</v>
+      </c>
+      <c r="C374" t="n">
+        <v>24</v>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>30</v>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G374"/>
+  <dimension ref="A1:G375"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11418,6 +11418,37 @@
         </is>
       </c>
     </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>5</v>
+      </c>
+      <c r="C375" t="n">
+        <v>24</v>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>30</v>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G375"/>
+  <dimension ref="A1:G376"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11449,6 +11449,41 @@
         </is>
       </c>
     </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>31</v>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G376"/>
+  <dimension ref="A1:G377"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11484,6 +11484,41 @@
         </is>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>31</v>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G377"/>
+  <dimension ref="A1:G378"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11519,6 +11519,41 @@
         </is>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>31</v>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G378"/>
+  <dimension ref="A1:G379"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11554,6 +11554,41 @@
         </is>
       </c>
     </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>33</v>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G379"/>
+  <dimension ref="A1:G380"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11589,6 +11589,41 @@
         </is>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>32</v>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G380"/>
+  <dimension ref="A1:G381"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11624,6 +11624,41 @@
         </is>
       </c>
     </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>34</v>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G381"/>
+  <dimension ref="A1:G382"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11659,6 +11659,41 @@
         </is>
       </c>
     </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>34</v>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G382"/>
+  <dimension ref="A1:G383"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11694,6 +11694,41 @@
         </is>
       </c>
     </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>34</v>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G383"/>
+  <dimension ref="A1:G384"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11729,6 +11729,41 @@
         </is>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>34</v>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G384"/>
+  <dimension ref="A1:G385"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11764,6 +11764,41 @@
         </is>
       </c>
     </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>36</v>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G385"/>
+  <dimension ref="A1:G388"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11799,6 +11799,115 @@
         </is>
       </c>
     </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>29</v>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G388"/>
+  <dimension ref="A1:G389"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11908,6 +11908,41 @@
         </is>
       </c>
     </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>30</v>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G389"/>
+  <dimension ref="A1:G390"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11943,6 +11943,43 @@
         </is>
       </c>
     </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G390"/>
+  <dimension ref="A1:G391"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11980,6 +11980,43 @@
         </is>
       </c>
     </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G391"/>
+  <dimension ref="A1:G392"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -12017,6 +12017,43 @@
         </is>
       </c>
     </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_rankings.xlsx
+++ b/data/fractal_rankings.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G392"/>
+  <dimension ref="A1:G393"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -12054,6 +12054,43 @@
         </is>
       </c>
     </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
